--- a/interview-mcp/data/knowledge/algorithm/docs/algorithm_pattern_study_system.xlsx
+++ b/interview-mcp/data/knowledge/algorithm/docs/algorithm_pattern_study_system.xlsx
@@ -1860,16 +1860,54 @@
       </c>
     </row>
     <row r="17" ht="37.5" customHeight="1">
-      <c r="A17" s="19" t="str"/>
-      <c r="B17" s="18" t="str"/>
-      <c r="C17" s="18" t="str"/>
-      <c r="D17" s="18" t="str"/>
-      <c r="E17" s="18" t="str"/>
-      <c r="F17" s="18" t="str"/>
-      <c r="G17" s="18" t="str"/>
-      <c r="H17" s="18" t="str"/>
-      <c r="I17" s="81" t="n"/>
-      <c r="J17" s="18" t="str"/>
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>Merge Sorted Array</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Two Pointers / Merge from Back</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Merging from the front overwrites elements in nums1 still needed. Writing right-to-left into the reserved tail slots avoids clobbering unread values.</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>Use three pointers (i = end of valid nums1, j = end of nums2, k = last slot). At each step place the larger element at k and move that pointer back. When the loop ends, any remaining nums2 elements must be copied; remaining nums1 elements are already in place.</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Forgetting to copy leftover nums2 elements after the main loop. Also: assuming leftover nums1 elements need to move — they are already correctly positioned.</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>Time O(m+n), Space O(1)</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="81" t="n">
+        <v>46189</v>
+      </c>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>7 days</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="37.5" customHeight="1">
       <c r="A18" s="19" t="str"/>
